--- a/files/九龙-牛头角及九龙湾-泰峰.xlsx
+++ b/files/九龙-牛头角及九龙湾-泰峰.xlsx
@@ -8,6 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2A座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2B座" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +45,102 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +151,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +232,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +665,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -37815,4 +38006,8175 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>A-DP</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1404呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>B | 1098呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1371呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>C | 1098呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>41&amp;42</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>A-DP | 3075呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 1893呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr"/>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>B | 1050呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>C | 1098呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr"/>
+      <c r="G8" s="21" t="inlineStr"/>
+      <c r="H8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr"/>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>B | 690呎 (3房)
+$1336万
+$19,359/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$525万
+$15,351/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>D | 470呎 (2房)
+$772万
+$16,426/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>E | 724呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1462万
+$19,500/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr"/>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>B | 690呎 (3房)
+$1267万
+$18,359/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$522万
+$15,260/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>D | 470呎 (2房)
+$774万
+$16,472/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>E | 723呎 (3房)
+$1412万
+$19,527/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1605万
+$21,400/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr"/>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>B | 690呎 (3房)
+$1168万
+$16,929/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$519万
+$15,170/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>D | 470呎 (2房)
+$763万
+$16,230/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>E | 723呎 (3房)
+$1376万
+$19,026/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1538万
+$20,500/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr"/>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>B | 690呎 (3房)
+$1145万
+$16,597/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$516万
+$15,079/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>D | 470呎 (2房)
+$760万
+$16,181/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>E | 723呎 (3房)
+$1339万
+$18,526/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1522万
+$20,300/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr"/>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>B | 690呎 (3房)
+$1118万
+$16,205/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$513万
+$14,988/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>D | 470呎 (2房)
+$758万
+$16,132/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>E | 723呎 (3房)
+$1483万
+$20,515/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1328万
+$17,700/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr"/>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>B | 690呎 (3房)
+$1121万
+$16,251/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$511万
+$14,944/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>D | 470呎 (2房)
+$756万
+$16,083/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>E | 723呎 (3房)
+$1440万
+$19,913/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1314万
+$17,523/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr"/>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>B | 690呎 (3房)
+$1115万
+$16,161/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$510万
+$14,901/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>D | 470呎 (2房)
+$754万
+$16,034/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>E | 723呎 (3房)
+$1234万
+$17,068/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1310万
+$17,471/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr"/>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>B | 690呎 (3房)
+$1275万
+$18,478/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$508万
+$14,857/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>D | 470呎 (2房)
+$751万
+$15,985/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>E | 724呎 (3房)
+$1240万
+$17,131/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>A | 750呎 (3房)
+$1345万
+$17,936/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr"/>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>B | 690呎 (3房)
+$1132万
+$16,404/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$507万
+$14,813/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>D | 470呎 (2房)
+$749万
+$15,938/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>E | 724呎 (3房)
+$1237万
+$17,080/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>A | 712呎 (3房)
+$1314万
+$18,450/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr"/>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>B | 652呎 (3房)
+$1121万
+$17,193/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$505万
+$14,769/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>D | 470呎 (2房)
+$747万
+$15,891/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>E | 686呎 (3房)
+$1233万
+$17,980/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 671呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr"/>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>B | 527呎 (2房)
+$871万
+$16,531/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>C | 378呎 (1房)
+$552万
+$14,593/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>D | 471呎 (2房)
+$746万
+$15,845/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>E | 549呎 (2房)
+$870万
+$15,845/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>F | 561呎 (2房)
+$889万
+$15,845/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>A | 671呎 (2房)
+$1137万
+$16,951/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr"/>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>B | 527呎 (2房)
+$834万
+$15,833/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>C | 378呎 (1房)
+$549万
+$14,519/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>D | 471呎 (2房)
+$743万
+$15,766/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>E | 549呎 (2房)
+$866万
+$15,767/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>F | 561呎 (2房)
+$884万
+$15,766/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 671呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr"/>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>B | 527呎 (2房)
+$830万
+$15,753/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>C | 378呎 (1房)
+$546万
+$14,444/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>D | 471呎 (2房)
+$758万
+$16,096/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>E | 549呎 (2房)
+$861万
+$15,689/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>F | 561呎 (2房)
+$880万
+$15,688/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>A | 671呎 (2房)
+$1131万
+$16,851/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr"/>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>B | 527呎 (2房)
+$826万
+$15,676/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>C | 378呎 (1房)
+$543万
+$14,376/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>D | 471呎 (2房)
+$735万
+$15,611/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>E | 549呎 (2房)
+$857万
+$15,610/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>F | 561呎 (2房)
+$876万
+$15,610/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 671呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr"/>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>B | 527呎 (2房)
+$822万
+$15,598/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>C | 378呎 (1房)
+$541万
+$14,302/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>D | 471呎 (2房)
+$732万
+$15,533/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>E | 549呎 (2房)
+$853万
+$15,532/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>F | 561呎 (2房)
+$871万
+$15,533/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>A | 671呎 (2房)
+$1169万
+$17,419/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr"/>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>B | 527呎 (2房)
+$818万
+$15,520/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>C | 378呎 (1房)
+$538万
+$14,230/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>D | 471呎 (2房)
+$728万
+$15,456/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>E | 549呎 (2房)
+$937万
+$17,062/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>F | 561呎 (2房)
+$867万
+$15,455/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>A | 671呎 (2房)
+$1155万
+$17,219/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr"/>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>B | 527呎 (2房)
+$814万
+$15,442/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>C | 378呎 (1房)
+$535万
+$14,161/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>D | 470呎 (2房)
+$724万
+$15,413/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>E | 549呎 (2房)
+$844万
+$15,379/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>F | 561呎 (2房)
+$863万
+$15,378/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>A | 671呎 (2房)
+$1127万
+$16,800/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr"/>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>B | 527呎 (2房)
+$831万
+$15,765/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>C | 378呎 (1房)
+$546万
+$14,458/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>D | 471呎 (2房)
+$721万
+$15,301/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>E | 549呎 (2房)
+$840万
+$15,302/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>F | 561呎 (2房)
+$858万
+$15,303/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>A | 671呎 (2房)
+$1138万
+$16,964/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr"/>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>B | 527呎 (2房)
+$806万
+$15,288/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>C | 378呎 (1房)
+$530万
+$14,021/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>D | 471呎 (2房)
+$717万
+$15,225/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>E | 549呎 (2房)
+$847万
+$15,423/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>F | 561呎 (2房)
+$854万
+$15,226/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>A | 671呎 (2房)
+$1153万
+$17,179/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr"/>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>B | 527呎 (2房)
+$802万
+$15,213/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>C | 378呎 (1房)
+$527万
+$13,950/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>D | 471呎 (2房)
+$714万
+$15,151/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>E | 549呎 (2房)
+$832万
+$15,151/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>F | 561呎 (2房)
+$850万
+$15,152/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>A | 671呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr"/>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>B | 527呎 (2房)
+$798万
+$15,137/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>C | 378呎 (1房)
+$525万
+$13,881/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>D | 471呎 (2房)
+$710万
+$15,074/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>E | 549呎 (2房)
+$828万
+$15,075/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>F | 561呎 (2房)
+$846万
+$15,075/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>A | 671呎 (2房)
+$1094万
+$16,300/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr"/>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>B | 527呎 (2房)
+$794万
+$15,063/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>C | 378呎 (1房)
+$522万
+$13,812/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>D | 471呎 (2房)
+$706万
+$15,000/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>E | 549呎 (2房)
+$824万
+$15,000/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>F | 561呎 (2房)
+$842万
+$15,000/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>A | 671呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr"/>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>B | 527呎 (2房)
+$790万
+$14,987/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>C | 378呎 (1房)
+$520万
+$13,743/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>D | 471呎 (2房)
+$703万
+$14,926/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>E | 549呎 (2房)
+$819万
+$14,925/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>F | 561呎 (2房)
+$837万
+$14,925/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>A | 671呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr"/>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>B | 527呎 (2房)
+$786万
+$14,913/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>C | 378呎 (1房)
+$517万
+$13,675/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>D | 471呎 (2房)
+$700万
+$14,851/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>E | 549呎 (2房)
+$796万
+$14,490/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>F | 561呎 (2房)
+$813万
+$14,490/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>A | 671呎 (2房)
+$1067万
+$15,900/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr"/>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>B | 527呎 (2房)
+$778万
+$14,765/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>C | 378呎 (1房)
+$512万
+$13,540/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>D | 470呎 (2房)
+$696万
+$14,809/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>E | 549呎 (2房)
+$788万
+$14,348/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>F | 561呎 (2房)
+$805万
+$14,348/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>A | 671呎 (2房)
+$1108万
+$16,519/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr"/>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>B | 527呎 (2房)
+$770万
+$14,619/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>C | 378呎 (1房)
+$507万
+$13,407/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>D | 471呎 (2房)
+$693万
+$14,705/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>E | 549呎 (2房)
+$780万
+$14,206/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>F | 561呎 (2房)
+$797万
+$14,205/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>A | 671呎 (2房)
+$1078万
+$16,060/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="inlineStr"/>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>B | 527呎 (2房)
+$763万
+$14,474/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>C | 378呎 (1房)
+$508万
+$13,447/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>D | 471呎 (2房)
+$689万
+$14,631/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>E | 549呎 (2房)
+$772万
+$14,066/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>F | 561呎 (2房)
+$789万
+$14,064/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>A | 671呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="inlineStr"/>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>B | 527呎 (2房)
+$755万
+$14,330/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>C | 378呎 (1房)
+$497万
+$13,143/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>D | 471呎 (2房)
+$695万
+$14,747/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>E | 549呎 (2房)
+$844万
+$15,372/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
+        <is>
+          <t>F | 561呎 (2房)
+$781万
+$13,925/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>A | 633呎 (3房)
+$1073万
+$16,950/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C37" s="21" t="inlineStr"/>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>B | 527呎 (2房)
+$748万
+$14,190/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="inlineStr">
+        <is>
+          <t>C | 378呎 (1房)
+$491万
+$12,981/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>D | 471呎 (2房)
+$682万
+$14,484/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>E | 511呎 (2房)
+$771万
+$15,088/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H37" s="24" t="inlineStr">
+        <is>
+          <t>F | 523呎 (2房)
+$788万
+$15,073/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>A-DP</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1126呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="21" t="inlineStr"/>
+      <c r="J5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1266呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+      <c r="I6" s="21" t="inlineStr"/>
+      <c r="J6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>41&amp;42</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>A-DP | 2997呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr"/>
+      <c r="I7" s="21" t="inlineStr"/>
+      <c r="J7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>A | 1309呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr"/>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>B | 1020呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>C | 1084呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr"/>
+      <c r="G8" s="21" t="inlineStr"/>
+      <c r="H8" s="21" t="inlineStr"/>
+      <c r="I8" s="21" t="inlineStr"/>
+      <c r="J8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>A | 734呎 (3房)
+$1310万
+$17,847/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr"/>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>B | 724呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>C | 460呎 (2房)
+$821万
+$17,841/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>D | 470呎 (2房)
+$860万
+$18,296/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$866万
+$18,473/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$913万
+$19,500/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$834万
+$16,891/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J9" s="24" t="inlineStr">
+        <is>
+          <t>H | 501呎 (2房)
+$868万
+$17,335/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>A | 734呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr"/>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>B | 723呎 (3房)
+$1339万
+$18,520/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>C | 460呎 (2房)
+$805万
+$17,491/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>D | 470呎 (2房)
+$822万
+$17,485/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$925万
+$19,721/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$836万
+$17,853/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$818万
+$16,559/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="J10" s="24" t="inlineStr">
+        <is>
+          <t>H | 501呎 (2房)
+$887万
+$17,697/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>A | 734呎 (3房)
+$1575万
+$21,452/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr"/>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>B | 723呎 (3房)
+$1286万
+$17,786/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>C | 460呎 (2房)
+$789万
+$17,148/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>D | 470呎 (2房)
+$818万
+$17,398/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$868万
+$18,499/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$823万
+$17,590/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$813万
+$16,460/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="J11" s="24" t="inlineStr">
+        <is>
+          <t>H | 501呎 (2房)
+$878万
+$17,521/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>A | 734呎 (3房)
+$1358万
+$18,500/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr"/>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>B | 724呎 (3房)
+$1260万
+$17,400/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>C | 460呎 (2房)
+$784万
+$17,046/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>D | 470呎 (2房)
+$814万
+$17,311/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$820万
+$17,480/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$819万
+$17,502/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$811万
+$16,411/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="J12" s="24" t="inlineStr">
+        <is>
+          <t>H | 501呎 (2房)
+$856万
+$17,078/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>A | 734呎 (3房)
+$1321万
+$18,000/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr"/>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>B | 723呎 (3房)
+$1264万
+$17,486/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>C | 460呎 (2房)
+$779万
+$16,943/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>D | 470呎 (2房)
+$810万
+$17,226/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$837万
+$17,844/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$804万
+$17,175/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$808万
+$16,362/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="J13" s="24" t="inlineStr">
+        <is>
+          <t>H | 501呎 (2房)
+$861万
+$17,178/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 734呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr"/>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>B | 723呎 (3房)
+$1344万
+$18,582/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>C | 460呎 (2房)
+$775万
+$16,843/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>D | 470呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$833万
+$17,755/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$832万
+$17,780/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$806万
+$16,314/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="J14" s="24" t="inlineStr">
+        <is>
+          <t>H | 501呎 (2房)
+$852万
+$17,008/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>A | 734呎 (3房)
+$1256万
+$17,114/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr"/>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>B | 723呎 (3房)
+$1239万
+$17,136/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>C | 460呎 (2房)
+$770万
+$16,743/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>D | 470呎 (2房)
+$802万
+$17,055/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$808万
+$17,220/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$807万
+$17,244/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$804万
+$16,265/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="J15" s="24" t="inlineStr">
+        <is>
+          <t>H | 501呎 (2房)
+$848万
+$16,924/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>A | 734呎 (3房)
+$1252万
+$17,064/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr"/>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>B | 723呎 (3房)
+$1235万
+$17,085/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>C | 460呎 (2房)
+$768万
+$16,693/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>D | 470呎 (2房)
+$799万
+$17,004/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$805万
+$17,168/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$805万
+$17,192/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$801万
+$16,217/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="J16" s="24" t="inlineStr">
+        <is>
+          <t>H | 501呎 (2房)
+$845万
+$16,874/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>A | 734呎 (3房)
+$1245万
+$16,964/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr"/>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>B | 723呎 (3房)
+$1228万
+$16,985/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>C | 460呎 (2房)
+$766万
+$16,646/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>D | 470呎 (2房)
+$797万
+$16,953/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$803万
+$17,117/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$802万
+$17,141/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$799万
+$16,168/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="J17" s="24" t="inlineStr">
+        <is>
+          <t>H | 501呎 (2房)
+$843万
+$16,824/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>A | 696呎 (3房)
+$1251万
+$17,980/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr"/>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>B | 686呎 (3房)
+$1233万
+$17,980/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>C | 460呎 (2房)
+$744万
+$16,176/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>D | 470呎 (2房)
+$818万
+$17,394/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$800万
+$17,066/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$800万
+$17,090/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$798万
+$16,160/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="J18" s="24" t="inlineStr">
+        <is>
+          <t>H | 463呎 (2房)
+$843万
+$18,214/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>A | 554呎 (2房)
+$898万
+$16,209/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr"/>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$872万
+$15,845/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>C | 465呎 (2房)
+$771万
+$16,581/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$802万
+$16,851/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$800万
+$17,049/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$799万
+$17,073/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$810万
+$16,389/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J19" s="24" t="inlineStr">
+        <is>
+          <t>H | 503呎 (2房)
+$841万
+$16,724/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>A | 554呎 (2房)
+$989万
+$17,854/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr"/>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$867万
+$15,767/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>C | 465呎 (2房)
+$767万
+$16,497/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$798万
+$16,767/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$796万
+$16,964/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$797万
+$17,030/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$802万
+$16,227/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="J20" s="24" t="inlineStr">
+        <is>
+          <t>H | 503呎 (2房)
+$837万
+$16,640/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>A | 554呎 (2房)
+$894万
+$16,137/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr"/>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$863万
+$15,689/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>C | 465呎 (2房)
+$763万
+$16,415/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>D | 475呎 (2房)
+$794万
+$16,718/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$792万
+$16,881/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$795万
+$16,987/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$778万
+$15,755/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="J21" s="24" t="inlineStr">
+        <is>
+          <t>H | 503呎 (2房)
+$833万
+$16,557/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>A | 554呎 (2房)
+$904万
+$16,310/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr"/>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$859万
+$15,611/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>C | 465呎 (2房)
+$740万
+$15,920/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$790万
+$16,601/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$788万
+$16,795/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$794万
+$16,955/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$774万
+$15,676/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="J22" s="24" t="inlineStr">
+        <is>
+          <t>H | 503呎 (2房)
+$861万
+$17,117/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>A | 554呎 (2房)
+$890万
+$16,074/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr"/>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$854万
+$15,533/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>C | 465呎 (2房)
+$737万
+$15,841/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>D | 475呎 (2房)
+$786万
+$16,552/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$784万
+$16,712/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$790万
+$16,870/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$771万
+$15,599/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="J23" s="24" t="inlineStr">
+        <is>
+          <t>H | 503呎 (2房)
+$825万
+$16,394/呎
+(24年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>A | 554呎 (2房)
+$886万
+$15,995/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr"/>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$872万
+$15,856/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>C | 465呎 (2房)
+$733万
+$15,761/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>D | 475呎 (2房)
+$813万
+$17,112/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$780万
+$16,629/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$786万
+$16,786/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$767万
+$15,520/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J24" s="24" t="inlineStr">
+        <is>
+          <t>H | 503呎 (2房)
+$820万
+$16,312/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>A | 554呎 (2房)
+$882万
+$15,915/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr"/>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$868万
+$15,778/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>C | 465呎 (2房)
+$729万
+$15,684/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>D | 475呎 (2房)
+$778万
+$16,387/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$776万
+$16,548/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$782万
+$16,703/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$763万
+$15,443/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J25" s="24" t="inlineStr">
+        <is>
+          <t>H | 503呎 (2房)
+$816万
+$16,231/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>A | 554呎 (2房)
+$877万
+$15,836/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr"/>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$842万
+$15,302/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>C | 465呎 (2房)
+$726万
+$15,606/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>D | 475呎 (2房)
+$775万
+$16,307/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$772万
+$16,465/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$778万
+$16,620/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$789万
+$15,966/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="J26" s="24" t="inlineStr">
+        <is>
+          <t>H | 503呎 (2房)
+$812万
+$16,149/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>A | 554呎 (2房)
+$873万
+$15,758/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr"/>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$859万
+$15,622/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>C | 465呎 (2房)
+$750万
+$16,133/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>D | 475呎 (2房)
+$801万
+$16,859/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$768万
+$16,384/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$774万
+$16,538/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$755万
+$15,289/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J27" s="24" t="inlineStr">
+        <is>
+          <t>H | 503呎 (2房)
+$808万
+$16,070/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>A | 554呎 (2房)
+$869万
+$15,679/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr"/>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$833万
+$15,151/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>C | 465呎 (2房)
+$718万
+$15,449/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>D | 475呎 (2房)
+$767万
+$16,145/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$765万
+$16,303/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$770万
+$16,455/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$781万
+$15,808/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="J28" s="24" t="inlineStr">
+        <is>
+          <t>H | 503呎 (2房)
+$804万
+$15,990/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>A | 554呎 (2房)
+$864万
+$15,601/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr"/>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$829万
+$15,075/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>C | 465呎 (2房)
+$715万
+$15,374/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>D | 475呎 (2房)
+$763万
+$16,065/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$761万
+$16,220/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$766万
+$16,374/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$748万
+$15,140/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="J29" s="24" t="inlineStr">
+        <is>
+          <t>H | 503呎 (2房)
+$800万
+$15,911/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>A | 554呎 (2房)
+$860万
+$15,523/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr"/>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$846万
+$15,389/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>C | 465呎 (2房)
+$711万
+$15,297/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>D | 475呎 (2房)
+$759万
+$15,985/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$757万
+$16,139/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$762万
+$16,293/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$744万
+$15,065/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="J30" s="24" t="inlineStr">
+        <is>
+          <t>H | 503呎 (2房)
+$796万
+$15,831/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>A | 554呎 (2房)
+$856万
+$15,446/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr"/>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$906万
+$16,476/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>C | 465呎 (2房)
+$708万
+$15,219/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$756万
+$15,872/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$753万
+$16,060/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$788万
+$16,844/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$740万
+$14,988/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="J31" s="24" t="inlineStr">
+        <is>
+          <t>H | 503呎 (2房)
+$792万
+$15,751/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>A | 554呎 (2房)
+$831万
+$14,996/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr"/>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$807万
+$14,678/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>C | 465呎 (2房)
+$704万
+$15,146/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>D | 475呎 (2房)
+$752万
+$15,825/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$749万
+$15,979/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$755万
+$16,130/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$737万
+$14,913/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="J32" s="24" t="inlineStr">
+        <is>
+          <t>H | 503呎 (2房)
+$799万
+$15,889/呎
+(24年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>A | 554呎 (2房)
+$823万
+$14,848/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr"/>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$789万
+$14,347/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>C | 465呎 (2房)
+$701万
+$15,069/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>D | 475呎 (2房)
+$748万
+$15,747/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$746万
+$15,900/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$771万
+$16,466/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$722万
+$14,621/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="J33" s="24" t="inlineStr">
+        <is>
+          <t>H | 503呎 (2房)
+$791万
+$15,730/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>A | 554呎 (2房)
+$814万
+$14,700/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr"/>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$781万
+$14,205/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>C | 465呎 (2房)
+$697万
+$14,996/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>D | 475呎 (2房)
+$744万
+$15,669/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$742万
+$15,821/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$747万
+$15,970/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$719万
+$14,549/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="J34" s="24" t="inlineStr">
+        <is>
+          <t>H | 503呎 (2房)
+$754万
+$14,992/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>A | 554呎 (2房)
+$806万
+$14,556/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="inlineStr"/>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$774万
+$14,065/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>C | 465呎 (2房)
+$694万
+$14,920/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>D | 475呎 (2房)
+$741万
+$15,592/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$738万
+$15,742/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$744万
+$15,891/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$715万
+$14,478/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J35" s="24" t="inlineStr">
+        <is>
+          <t>H | 503呎 (2房)
+$776万
+$15,421/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>A | 554呎 (2房)
+$798万
+$14,412/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="inlineStr"/>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>B | 550呎 (2房)
+$786万
+$14,287/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>C | 465呎 (2房)
+$711万
+$15,290/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$737万
+$15,481/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$735万
+$15,663/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$740万
+$15,812/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I36" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$712万
+$14,405/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J36" s="24" t="inlineStr">
+        <is>
+          <t>H | 503呎 (2房)
+$749万
+$14,887/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>A | 516呎 (2房)
+$806万
+$15,620/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C37" s="21" t="inlineStr"/>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>B | 512呎 (2房)
+$772万
+$15,084/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="inlineStr">
+        <is>
+          <t>C | 465呎 (2房)
+$687万
+$14,772/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>D | 476呎 (2房)
+$733万
+$15,403/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>E | 469呎 (2房)
+$731万
+$15,584/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H37" s="24" t="inlineStr">
+        <is>
+          <t>F | 468呎 (2房)
+$755万
+$16,141/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I37" s="24" t="inlineStr">
+        <is>
+          <t>G | 494呎 (2房)
+$708万
+$14,332/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J37" s="24" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+$741万
+$15,929/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>A-DP</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>B-DP</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>41&amp;42</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>A-DP | 3415呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>B-DP | 1839呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="21" t="inlineStr"/>
+      <c r="J5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 1479呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>B | 834呎 (3房)
+$1835万
+$22,000/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>C | 845呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+      <c r="I6" s="21" t="inlineStr"/>
+      <c r="J6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>A | 732呎 (3房)
+$1318万
+$18,000/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>B | 774呎 (3房)
+$1430万
+$18,481/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>C | 560呎 (3房)
+$1002万
+$17,900/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t>D | 279呎 (开放式)
+$422万
+$15,118/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$558万
+$16,561/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t>F | 379呎 (1房)
+$609万
+$16,061/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>A | 732呎 (3房)
+$1281万
+$17,497/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr"/>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>B | 774呎 (3房)
+$1612万
+$20,826/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr"/>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>C | 560呎 (3房)
+$1021万
+$18,231/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>D | 279呎 (开放式)
+$424万
+$15,190/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$556万
+$16,510/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>F | 379呎 (1房)
+$607万
+$16,013/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>A | 732呎 (3房)
+$1222万
+$16,700/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr"/>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>B | 774呎 (3房)
+$1393万
+$18,000/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr"/>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>C | 560呎 (3房)
+$983万
+$17,550/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>D | 279呎 (开放式)
+$417万
+$14,939/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$555万
+$16,460/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>F | 379呎 (1房)
+$605万
+$15,966/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>A | 732呎 (3房)
+$1201万
+$16,413/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr"/>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>B | 774呎 (3房)
+$1362万
+$17,597/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr"/>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>C | 560呎 (3房)
+$966万
+$17,250/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>D | 279呎 (开放式)
+$419万
+$15,025/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$553万
+$16,409/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>F | 379呎 (1房)
+$603万
+$15,918/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>A | 732呎 (3房)
+$1190万
+$16,259/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr"/>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>B | 774呎 (3房)
+$1528万
+$19,748/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr"/>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>C | 560呎 (3房)
+$969万
+$17,300/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>D | 280呎 (开放式)
+$417万
+$14,896/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$551万
+$16,359/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>F | 379呎 (1房)
+$617万
+$16,282/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>A | 732呎 (3房)
+$1373万
+$18,759/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr"/>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>B | 774呎 (3房)
+$1507万
+$19,476/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr"/>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>C | 560呎 (3房)
+$963万
+$17,200/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>D | 279呎 (开放式)
+$415万
+$14,875/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$550万
+$16,312/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>F | 379呎 (1房)
+$600万
+$15,823/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>A | 732呎 (3房)
+$1183万
+$16,161/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr"/>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>B | 774呎 (3房)
+$1319万
+$17,047/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr"/>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>C | 560呎 (3房)
+$958万
+$17,100/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>D | 279呎 (开放式)
+$413万
+$14,799/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$548万
+$16,264/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>F | 379呎 (1房)
+$598万
+$15,776/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>A | 732呎 (3房)
+$1170万
+$15,977/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr"/>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>B | 774呎 (3房)
+$1313万
+$16,961/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr"/>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>C | 560呎 (3房)
+$952万
+$17,000/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>D | 279呎 (开放式)
+$411万
+$14,724/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$546万
+$16,217/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>F | 379呎 (1房)
+$596万
+$15,728/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>A | 732呎 (3房)
+$1176万
+$16,066/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr"/>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>B | 774呎 (3房)
+$870万
+$11,239/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr"/>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>C | 560呎 (3房)
+$946万
+$16,900/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>D | 279呎 (开放式)
+$410万
+$14,681/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$545万
+$16,169/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>F | 379呎 (1房)
+$594万
+$15,681/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>A | 694呎 (3房)
+$1184万
+$17,056/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr"/>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>B | 737呎 (3房)
+$1312万
+$17,800/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr"/>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>C | 560呎 (3房)
+$962万
+$17,180/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>D | 279呎 (开放式)
+$408万
+$14,638/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>E | 337呎 (1房)
+$543万
+$16,122/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>F | 379呎 (1房)
+$600万
+$15,836/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="J16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>A | 514呎 (2房)
+$766万
+$14,905/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr"/>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>B | 508呎 (2房)
+$809万
+$15,925/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr"/>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>C | 664呎 (2房)
+$1116万
+$16,800/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>D | 560呎 (3房)
+$958万
+$17,109/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>E | 278呎 (开放式)
+$406万
+$14,594/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$542万
+$16,074/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="J17" s="24" t="inlineStr">
+        <is>
+          <t>G | 373呎 (1房)
+$581万
+$15,587/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>A | 514呎 (2房)
+$762万
+$14,831/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr"/>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>B | 508呎 (2房)
+$805万
+$15,844/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr"/>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>C | 664呎 (2房)
+$1113万
+$16,760/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>D | 560呎 (3房)
+$945万
+$16,880/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>E | 278呎 (开放式)
+$404万
+$14,522/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$539万
+$15,994/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J18" s="24" t="inlineStr">
+        <is>
+          <t>G | 373呎 (1房)
+$578万
+$15,509/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>A | 514呎 (2房)
+$758万
+$14,757/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr"/>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>B | 508呎 (2房)
+$832万
+$16,380/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr"/>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>C | 664呎 (2房)
+$1099万
+$16,549/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>D | 560呎 (3房)
+$952万
+$17,009/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>E | 278呎 (开放式)
+$417万
+$15,011/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$536万
+$15,914/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J19" s="24" t="inlineStr">
+        <is>
+          <t>G | 373呎 (1房)
+$576万
+$15,432/呎
+(24年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>A | 514呎 (2房)
+$755万
+$14,685/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr"/>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>B | 508呎 (2房)
+$828万
+$16,299/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr"/>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>C | 664呎 (2房)
+$1092万
+$16,449/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>D | 560呎 (3房)
+$940万
+$16,780/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>E | 278呎 (开放式)
+$400万
+$14,378/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$534万
+$15,837/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J20" s="24" t="inlineStr">
+        <is>
+          <t>G | 373呎 (1房)
+$573万
+$15,357/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>A | 514呎 (2房)
+$761万
+$14,802/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr"/>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>B | 508呎 (2房)
+$793万
+$15,608/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr"/>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>C | 664呎 (2房)
+$1096万
+$16,500/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>D | 560呎 (3房)
+$937万
+$16,730/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>E | 278呎 (开放式)
+$398万
+$14,306/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$531万
+$15,757/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J21" s="24" t="inlineStr">
+        <is>
+          <t>G | 373呎 (1房)
+$570万
+$15,279/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>A | 514呎 (2房)
+$747万
+$14,537/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr"/>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>B | 508呎 (2房)
+$820万
+$16,136/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr"/>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>C | 664呎 (2房)
+$1109万
+$16,700/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>D | 560呎 (3房)
+$934万
+$16,680/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>E | 278呎 (开放式)
+$396万
+$14,234/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$528万
+$15,680/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J22" s="24" t="inlineStr">
+        <is>
+          <t>G | 373呎 (1房)
+$567万
+$15,204/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>A | 514呎 (2房)
+$753万
+$14,654/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr"/>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>B | 508呎 (2房)
+$785万
+$15,455/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr"/>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>C | 664呎 (2房)
+$1104万
+$16,634/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>D | 560呎 (3房)
+$931万
+$16,630/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>E | 278呎 (开放式)
+$394万
+$14,162/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$526万
+$15,599/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J23" s="24" t="inlineStr">
+        <is>
+          <t>G | 373呎 (1房)
+$564万
+$15,129/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>A | 514呎 (2房)
+$817万
+$15,889/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr"/>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>B | 508呎 (2房)
+$781万
+$15,376/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr"/>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>C | 664呎 (2房)
+$1101万
+$16,583/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>D | 560呎 (3房)
+$930万
+$16,600/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>E | 278呎 (开放式)
+$392万
+$14,090/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$523万
+$15,522/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J24" s="24" t="inlineStr">
+        <is>
+          <t>G | 373呎 (1房)
+$561万
+$15,051/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>A | 514呎 (2房)
+$736万
+$14,321/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr"/>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>B | 508呎 (2房)
+$777万
+$15,301/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr"/>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>C | 664呎 (2房)
+$1066万
+$16,051/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>D | 560呎 (3房)
+$926万
+$16,530/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>E | 278呎 (开放式)
+$390万
+$14,022/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$520万
+$15,445/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J25" s="24" t="inlineStr">
+        <is>
+          <t>G | 373呎 (1房)
+$559万
+$14,979/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>A | 514呎 (2房)
+$732万
+$14,251/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr"/>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>B | 508呎 (2房)
+$804万
+$15,819/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr"/>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>C | 664呎 (2房)
+$1062万
+$16,000/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>D | 560呎 (3房)
+$923万
+$16,480/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>E | 278呎 (开放式)
+$388万
+$13,953/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$518万
+$15,368/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J26" s="24" t="inlineStr">
+        <is>
+          <t>G | 373呎 (1房)
+$556万
+$14,903/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>A | 514呎 (2房)
+$729万
+$14,179/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr"/>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>B | 508呎 (2房)
+$800万
+$15,740/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr"/>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>C | 664呎 (2房)
+$1065万
+$16,039/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>D | 560呎 (3房)
+$918万
+$16,393/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>E | 278呎 (开放式)
+$386万
+$13,885/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$515万
+$15,291/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J27" s="24" t="inlineStr">
+        <is>
+          <t>G | 373呎 (1房)
+$553万
+$14,828/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>A | 514呎 (2房)
+$725万
+$14,109/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr"/>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>B | 508呎 (2房)
+$796万
+$15,661/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr"/>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>C | 664呎 (2房)
+$1044万
+$15,717/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>D | 560呎 (3房)
+$945万
+$16,871/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>E | 278呎 (开放式)
+$384万
+$13,813/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$513万
+$15,217/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J28" s="24" t="inlineStr">
+        <is>
+          <t>G | 373呎 (1房)
+$608万
+$16,290/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>A | 514呎 (2房)
+$722万
+$14,039/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr"/>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>B | 508呎 (2房)
+$762万
+$15,000/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr"/>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>C | 664呎 (2房)
+$1071万
+$16,133/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>D | 560呎 (3房)
+$916万
+$16,350/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>E | 278呎 (开放式)
+$392万
+$14,101/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$510万
+$15,139/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J29" s="24" t="inlineStr">
+        <is>
+          <t>G | 373呎 (1房)
+$548万
+$14,681/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>A | 514呎 (2房)
+$701万
+$13,630/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr"/>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>B | 508呎 (2房)
+$768万
+$15,128/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr"/>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>C | 664呎 (2房)
+$1060万
+$15,964/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>D | 560呎 (3房)
+$910万
+$16,250/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>E | 278呎 (开放式)
+$425万
+$15,273/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$508万
+$15,065/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J30" s="24" t="inlineStr">
+        <is>
+          <t>G | 373呎 (1房)
+$545万
+$14,609/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>A | 514呎 (2房)
+$694万
+$13,494/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr"/>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>B | 508呎 (2房)
+$732万
+$14,417/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr"/>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>C | 664呎 (2房)
+$1046万
+$15,750/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>D | 560呎 (3房)
+$904万
+$16,150/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>E | 278呎 (开放式)
+$378万
+$13,608/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$532万
+$15,801/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="J31" s="24" t="inlineStr">
+        <is>
+          <t>G | 373呎 (1房)
+$534万
+$14,322/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>A | 514呎 (2房)
+$696万
+$13,535/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr"/>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>B | 508呎 (2房)
+$753万
+$14,829/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr"/>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>C | 664呎 (2房)
+$1042万
+$15,700/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>D | 560呎 (3房)
+$899万
+$16,050/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>E | 278呎 (开放式)
+$416万
+$14,950/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$495万
+$14,697/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J32" s="24" t="inlineStr">
+        <is>
+          <t>G | 373呎 (1房)
+$529万
+$14,180/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>A | 514呎 (2房)
+$680万
+$13,230/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr"/>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>B | 508呎 (2房)
+$746万
+$14,685/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr"/>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>C | 664呎 (2房)
+$993万
+$14,949/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>D | 560呎 (3房)
+$885万
+$15,800/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>E | 278呎 (开放式)
+$414万
+$14,874/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$493万
+$14,623/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J33" s="24" t="inlineStr">
+        <is>
+          <t>G | 373呎 (1房)
+$524万
+$14,040/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>A | 514呎 (2房)
+$673万
+$13,097/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr"/>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>B | 508呎 (2房)
+$739万
+$14,539/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr"/>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>C | 664呎 (2房)
+$1010万
+$15,206/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>D | 560呎 (3房)
+$862万
+$15,396/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>E | 278呎 (开放式)
+$373万
+$13,406/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$490万
+$14,549/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J34" s="24" t="inlineStr">
+        <is>
+          <t>G | 372呎 (1房)
+$518万
+$13,938/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>A | 514呎 (2房)
+$667万
+$12,979/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="inlineStr"/>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>B | 508呎 (2房)
+$728万
+$14,337/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="inlineStr"/>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>C | 664呎 (2房)
+$959万
+$14,449/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>D | 560呎 (3房)
+$887万
+$15,841/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>E | 240呎 (开放式)
+$391万
+$16,300/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>F | 337呎 (1房)
+$488万
+$14,478/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="J35" s="24" t="inlineStr">
+        <is>
+          <t>G | 373呎 (1房)
+$485万
+$12,997/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1058呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 1447呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1168呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1447呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>A | 1052呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>B | 1447呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$558万
+$16,601/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$574万
+$17,086/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$588万
+$17,488/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>D | 429呎 (2房)
+$752万
+$17,522/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>E | 516呎 (2房)
+$852万
+$16,508/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$760万
+$16,486/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$556万
+$16,551/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$573万
+$17,054/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$584万
+$17,384/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>D | 429呎 (2房)
+$744万
+$17,350/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>E | 516呎 (2房)
+$849万
+$16,459/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$758万
+$16,436/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$554万
+$16,500/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$567万
+$16,884/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$592万
+$17,613/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>D | 429呎 (2房)
+$748万
+$17,438/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>E | 516呎 (2房)
+$847万
+$16,411/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$755万
+$16,386/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$553万
+$16,449/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$566万
+$16,833/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$579万
+$17,229/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>D | 429呎 (2房)
+$740万
+$17,247/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>E | 516呎 (2房)
+$844万
+$16,362/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$753万
+$16,336/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$551万
+$16,399/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$564万
+$16,783/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$580万
+$17,250/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>D | 429呎 (2房)
+$741万
+$17,266/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>E | 516呎 (2房)
+$842万
+$16,314/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$778万
+$16,866/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$549万
+$16,351/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$562万
+$16,732/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$577万
+$17,164/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>D | 429呎 (2房)
+$737万
+$17,179/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>E | 516呎 (2房)
+$839万
+$16,266/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$770万
+$16,698/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$548万
+$16,304/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$560万
+$16,682/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$574万
+$17,077/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>D | 429呎 (2房)
+$733万
+$17,093/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>E | 516呎 (2房)
+$837万
+$16,217/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$762万
+$16,534/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$546万
+$16,256/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$559万
+$16,631/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$572万
+$17,027/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>D | 429呎 (2房)
+$731万
+$17,042/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>E | 516呎 (2房)
+$834万
+$16,169/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$755万
+$16,371/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$566万
+$16,839/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$557万
+$16,580/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$570万
+$16,976/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>D | 429呎 (2房)
+$729万
+$16,991/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>E | 516呎 (2房)
+$814万
+$15,771/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$747万
+$16,208/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$543万
+$16,161/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$555万
+$16,530/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$569万
+$16,926/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>D | 429呎 (2房)
+$727万
+$16,939/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>E | 516呎 (2房)
+$829万
+$16,072/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$740万
+$16,048/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$527万
+$15,690/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$575万
+$17,119/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$567万
+$16,875/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>D | 428呎 (2房)
+$723万
+$16,886/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>E | 515呎 (2房)
+$820万
+$15,913/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>F | 273呎 (开放式)
+$430万
+$15,751/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>G | 287呎 (开放式)
+$443万
+$15,425/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$525万
+$15,613/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$551万
+$16,399/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$564万
+$16,792/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>D | 428呎 (2房)
+$719万
+$16,804/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>E | 515呎 (2房)
+$815万
+$15,833/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>F | 273呎 (开放式)
+$428万
+$15,674/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>G | 287呎 (开放式)
+$486万
+$16,941/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$536万
+$15,938/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$570万
+$16,952/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$561万
+$16,708/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>D | 428呎 (2房)
+$716万
+$16,720/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>E | 515呎 (2房)
+$811万
+$15,753/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>F | 273呎 (开放式)
+$426万
+$15,593/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>G | 286呎 (开放式)
+$438万
+$15,325/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$519万
+$15,455/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$560万
+$16,658/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$559万
+$16,625/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>D | 428呎 (2房)
+$712万
+$16,638/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>E | 515呎 (2房)
+$807万
+$15,676/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>F | 272呎 (开放式)
+$424万
+$15,574/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>G | 287呎 (开放式)
+$436万
+$15,195/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$517万
+$15,381/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$570万
+$16,952/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$584万
+$17,372/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>D | 428呎 (2房)
+$708万
+$16,554/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>E | 515呎 (2房)
+$814万
+$15,800/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>F | 272呎 (开放式)
+$422万
+$15,500/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>G | 287呎 (开放式)
+$434万
+$15,118/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$514万
+$15,304/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$540万
+$16,074/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$553万
+$16,461/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>D | 428呎 (2房)
+$726万
+$16,967/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>E | 515呎 (2房)
+$799万
+$15,520/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>F | 273呎 (开放式)
+$419万
+$15,363/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>G | 287呎 (开放式)
+$432万
+$15,045/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$512万
+$15,226/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$558万
+$16,619/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$572万
+$17,015/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>D | 428呎 (2房)
+$729万
+$17,028/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>E | 515呎 (2房)
+$795万
+$15,443/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>F | 273呎 (开放式)
+$417万
+$15,286/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>G | 287呎 (开放式)
+$430万
+$14,969/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$509万
+$15,152/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$556万
+$16,536/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$548万
+$16,298/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>D | 428呎 (2房)
+$725万
+$16,944/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>E | 515呎 (2房)
+$791万
+$15,365/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>F | 273呎 (开放式)
+$415万
+$15,209/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>G | 287呎 (开放式)
+$428万
+$14,895/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$520万
+$15,470/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$532万
+$15,836/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$545万
+$16,217/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>D | 428呎 (2房)
+$694万
+$16,227/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>E | 515呎 (2房)
+$787万
+$15,289/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>F | 273呎 (开放式)
+$429万
+$15,725/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>G | 286呎 (开放式)
+$425万
+$14,874/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$504万
+$15,003/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$688万
+$20,464/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$563万
+$16,762/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>D | 428呎 (2房)
+$718万
+$16,776/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>E | 515呎 (2房)
+$865万
+$16,794/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>F | 273呎 (开放式)
+$427万
+$15,645/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>G | 287呎 (开放式)
+$440万
+$15,324/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$502万
+$14,926/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$547万
+$16,289/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$539万
+$16,054/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>D | 428呎 (2房)
+$714万
+$16,694/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>E | 515呎 (2房)
+$780万
+$15,138/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>F | 273呎 (开放式)
+$409万
+$14,985/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>G | 287呎 (开放式)
+$438万
+$15,244/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$499万
+$14,854/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$545万
+$16,208/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$558万
+$16,598/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 428呎 (2房)
+$888万
+$20,759/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>E | 515呎 (2房)
+$776万
+$15,062/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>F | 272呎 (开放式)
+$423万
+$15,551/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>G | 287呎 (开放式)
+$419万
+$14,603/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$497万
+$14,780/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$542万
+$16,131/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$555万
+$16,515/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>D | 428呎 (2房)
+$707万
+$16,526/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>E | 515呎 (2房)
+$772万
+$14,986/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>F | 273呎 (开放式)
+$405万
+$14,835/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>G | 287呎 (开放式)
+$417万
+$14,530/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$494万
+$14,705/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$539万
+$16,048/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$531万
+$15,815/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>D | 428呎 (2房)
+$704万
+$16,444/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>E | 515呎 (2房)
+$768万
+$14,913/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>F | 273呎 (开放式)
+$397万
+$14,546/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>G | 287呎 (开放式)
+$415万
+$14,456/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$484万
+$14,417/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$661万
+$19,667/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$521万
+$15,506/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>D | 428呎 (2房)
+$690万
+$16,121/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>E | 515呎 (2房)
+$764万
+$14,839/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>F | 273呎 (开放式)
+$409万
+$14,978/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>G | 286呎 (开放式)
+$413万
+$14,434/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$482万
+$14,345/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$506万
+$15,068/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$518万
+$15,429/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>D | 428呎 (2房)
+$661万
+$15,439/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>E | 515呎 (2房)
+$760万
+$14,765/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>F | 273呎 (开放式)
+$407万
+$14,908/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>G | 287呎 (开放式)
+$411万
+$14,314/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$480万
+$14,274/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$523万
+$15,577/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$536万
+$15,952/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>D | 428呎 (2房)
+$683万
+$15,960/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>E | 515呎 (2房)
+$757万
+$14,691/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>F | 273呎 (开放式)
+$405万
+$14,835/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>G | 287呎 (开放式)
+$425万
+$14,794/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$477万
+$14,202/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$536万
+$15,964/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$533万
+$15,869/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>D | 428呎 (2房)
+$680万
+$15,881/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>E | 515呎 (2房)
+$782万
+$15,186/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>F | 273呎 (开放式)
+$396万
+$14,520/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>G | 287呎 (开放式)
+$414万
+$14,443/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>A | 336呎 (1房)
+$470万
+$13,991/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>B | 336呎 (1房)
+$517万
+$15,378/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>C | 336呎 (1房)
+$511万
+$15,199/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>D | 428呎 (2房)
+$651万
+$15,210/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>E | 477呎 (2房)
+$778万
+$16,300/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>F | 235呎 (开放式)
+$385万
+$16,400/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
+        <is>
+          <t>G | 249呎 (开放式)
+$429万
+$17,229/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-牛头角及九龙湾-泰峰.xlsx
+++ b/files/九龙-牛头角及九龙湾-泰峰.xlsx
@@ -665,7 +665,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -38171,12 +38171,33 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>41&amp;42</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>A-DP | 3075呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>B | 1371呎 (4+房)
 -
@@ -38184,7 +38205,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>C | 1098呎 (3房)
 -
@@ -38192,27 +38213,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>41&amp;42</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>A-DP | 3075呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
       <c r="F7" s="21" t="inlineStr"/>
       <c r="G7" s="21" t="inlineStr"/>
       <c r="H7" s="21" t="inlineStr"/>
@@ -39985,19 +39985,19 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>41&amp;42</t>
         </is>
       </c>
       <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>B | 1266呎 (4+房)
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>A-DP | 2997呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
       <c r="F6" s="21" t="inlineStr"/>
       <c r="G6" s="21" t="inlineStr"/>
@@ -40008,19 +40008,19 @@
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>41&amp;42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>A-DP | 2997呎 (4+房)
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1266呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
       <c r="F7" s="21" t="inlineStr"/>
       <c r="G7" s="21" t="inlineStr"/>

--- a/files/九龙-牛头角及九龙湾-泰峰.xlsx
+++ b/files/九龙-牛头角及九龙湾-泰峰.xlsx
@@ -670,7 +670,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -47098,7 +47098,7 @@
       </c>
       <c r="M745" s="3" t="inlineStr">
         <is>
-          <t>90天付款計劃</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N745" s="3" t="inlineStr">
@@ -47842,7 +47842,7 @@
       </c>
       <c r="M757" s="3" t="inlineStr">
         <is>
-          <t>90天付款計劃</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N757" s="3" t="inlineStr">
@@ -49268,7 +49268,7 @@
       </c>
       <c r="M780" s="3" t="inlineStr">
         <is>
-          <t>90天付款計劃</t>
+          <t>90天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N780" s="3" t="inlineStr">
